--- a/LanguageAndProfile-ManualTestCases.xlsx
+++ b/LanguageAndProfile-ManualTestCases.xlsx
@@ -3,12 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28627"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{50C48703-48DB-4490-8C86-8E36AD8DF5E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Language Test Cases" sheetId="5" r:id="rId1"/>
+    <sheet name="Skill Test Cases" sheetId="7" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -30,9 +31,393 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="110">
+  <si>
+    <t>Test Case ID</t>
+  </si>
+  <si>
+    <t>Test Case Title</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Preconditions</t>
+  </si>
+  <si>
+    <t>Test Steps</t>
+  </si>
+  <si>
+    <t>Test Data</t>
+  </si>
+  <si>
+    <t>Expected Results</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>TC_001</t>
+  </si>
+  <si>
+    <t>User can add a language</t>
+  </si>
+  <si>
+    <t>Verify that a user can add a language to their profile.</t>
+  </si>
+  <si>
+    <t>User is logged in to the Mars application and is on the Profiles Page with the Languages tab selected.</t>
+  </si>
+  <si>
+    <t>1. Click on 'Add New' button.
+2. Enter the language name in the 'Add Language' textbox.
+3. Select the language level from the drop-down 'Choose Language Level'.
+4. Click on 'Add' button.</t>
+  </si>
+  <si>
+    <t>Language Name: Spanish
+Language Level: Fluent</t>
+  </si>
+  <si>
+    <t>The "Add language" text box, the "Choose Language Level" drop down and the "Add" and "Cancel" buttons should disappear. The language should be added to the profile, and a confirmation pop-up should appear saying - "Spanish has been added to your languages"</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>TC_002</t>
+  </si>
+  <si>
+    <t>User can edit an existing language</t>
+  </si>
+  <si>
+    <t>Verify that a user can edit a language and its proficiency.</t>
+  </si>
+  <si>
+    <t>User is logged in to the Mars application and is on the Profiles Page with the Languages tab selected. User has at least one language added.</t>
+  </si>
+  <si>
+    <t>1. Click on the 'Edit' icon next to an existing language.
+2. Change the language and language level.
+3. Click on 'Update' button.</t>
+  </si>
+  <si>
+    <t>Language Name: Spanish
+New Language Name: French
+New Language Level: Native/Bilingual</t>
+  </si>
+  <si>
+    <t>The language and language level should be updated successfully, and a confirmation pop-up should appear saying - "French has been updated to your languages"</t>
+  </si>
+  <si>
+    <t>TC_003</t>
+  </si>
+  <si>
+    <t>User can delete a language</t>
+  </si>
+  <si>
+    <t>Verify that a user can delete a language from their profile.</t>
+  </si>
+  <si>
+    <t>1. Click on the 'Delete' icon next to a language.</t>
+  </si>
+  <si>
+    <t>Language Name: French </t>
+  </si>
+  <si>
+    <t>The language should be deleted from the profile, and a confirmation pop-up should appear saying - "French has been deleted from your languages"</t>
+  </si>
+  <si>
+    <t>TC_004</t>
+  </si>
+  <si>
+    <t>User can only add up to 4 languages</t>
+  </si>
+  <si>
+    <t>Verify that a user can only add up to 4 languages.</t>
+  </si>
+  <si>
+    <t>1. Add 4 languages to the profile one by one.
+2. Check if the 'Add New' button disappears.</t>
+  </si>
+  <si>
+    <t>Language Names: English, Spanish, German, French
+Language Levels: Native/Bilingual, Fluent, Conversational, Basic</t>
+  </si>
+  <si>
+    <t>The user should be able to add a maximum of 4 languages, and after that the 'Add New' button should disappear.</t>
+  </si>
+  <si>
+    <t>TC_005</t>
+  </si>
+  <si>
+    <t>User cannot add duplicate language with the same language level</t>
+  </si>
+  <si>
+    <t>Verify that a user cannot add a language if it already exists in their profile with the same proficiency level.</t>
+  </si>
+  <si>
+    <t>1. Click on 'Add New' button. 
+2. Enter the same language name in the 'Add Language' textbox (e.g., Spanish). 
+3. Select the same language level from the drop-down (e.g., Fluent). 
+4. Click on 'Add' button.</t>
+  </si>
+  <si>
+    <t>A pop-up message should appear saying: "This language is already exist in your language list." and the language should not be added to the profile.</t>
+  </si>
+  <si>
+    <t>TC_006</t>
+  </si>
+  <si>
+    <t>User cannot add same language with different proficiency level</t>
+  </si>
+  <si>
+    <t>Verify that a user cannot add a language with a different proficiency level if it already exists in the profile.</t>
+  </si>
+  <si>
+    <t>1. Click on 'Add New' button.
+2. Enter the same language name in the 'Add Language' textbox (e.g., Spanish).
+3. Select a different proficiency level from the drop-down (e.g., Basic).
+4. Click on 'Add' button.</t>
+  </si>
+  <si>
+    <t>Language Name: Spanish
+New Language Level: Basic</t>
+  </si>
+  <si>
+    <t>A pop-up message should appear saying: "Duplicated data" and the language should not be added to the profile.</t>
+  </si>
+  <si>
+    <t>TC_007</t>
+  </si>
+  <si>
+    <t>User cannot add empty language and proficiency level</t>
+  </si>
+  <si>
+    <t>Verify that the system shows an error message when a user tries to add an empty language or proficiency level.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User is logged in to the Mars application and is on the Profiles Page with the Languages tab selected. </t>
+  </si>
+  <si>
+    <t>1. Click on 'Add New' button.
+2. Leave the 'Add Language' textbox empty.
+3. Do not select a proficiency level.
+4. Click on 'Add' button.</t>
+  </si>
+  <si>
+    <t>Language Name: (Empty)
+Language Level: (Empty)</t>
+  </si>
+  <si>
+    <t>The system should display an error message: "Please enter language and level" and the language should not be added.</t>
+  </si>
+  <si>
+    <t>TC_008</t>
+  </si>
+  <si>
+    <t>User cannot add a language when clicked Cancel</t>
+  </si>
+  <si>
+    <t>Verify that the user is not able to add a language when clicked on "Cancel"</t>
+  </si>
+  <si>
+    <t>1. Click on 'Add New' button. 
+2. Enter the same language name in the 'Add Language' textbox (e.g., Spanish). 
+3. Select the same language level from the drop-down (e.g., Fluent). 
+4. Click on 'Cancel' button.</t>
+  </si>
+  <si>
+    <t>The "Add language" text box, the "Choose Language Level" drop down and the "Add" and "Cancel" buttons should disappear. The language should not be added to the profile.</t>
+  </si>
+  <si>
+    <t>TC_009</t>
+  </si>
+  <si>
+    <t>User cannot edit a language when clicked Cancel</t>
+  </si>
+  <si>
+    <t>Verify that a user cannot edit a language to their profile.</t>
+  </si>
+  <si>
+    <t>1. Click on the 'Edit' icon next to an existing language.
+2. Change the language and language level.
+3. Click on 'Cancel' button.</t>
+  </si>
+  <si>
+    <t>The language should not be updated and the text boxes should disappear.</t>
+  </si>
+  <si>
+    <t>User can add a skill</t>
+  </si>
+  <si>
+    <t>Verify that a user can add a skill to their profile.</t>
+  </si>
+  <si>
+    <t>User is logged in and on the Profile Page's Skills tab.</t>
+  </si>
+  <si>
+    <t>1. Click on 'Add New'.
+2. Enter a skill name.
+3. Select the skill level.
+4. Click on 'Add'.</t>
+  </si>
+  <si>
+    <t>Skill Name: "Java"
+Skill Level: "Advanced"</t>
+  </si>
+  <si>
+    <t>The skill should be added to the profile, and a confirmation message should appear: "Java" has been added to your skills.</t>
+  </si>
+  <si>
+    <t>User can edit a skill</t>
+  </si>
+  <si>
+    <t>Verify that a user can edit a skill name and level.</t>
+  </si>
+  <si>
+    <t>User has at least one skill added.</t>
+  </si>
+  <si>
+    <t>1. Click on the 'Edit' icon next to an existing skill.
+2. Edit the skill name and level.
+3. Click on 'Update'.</t>
+  </si>
+  <si>
+    <t>Skill Name: "Java"
+New Skill Name: "JavaScript"
+New Skill Level: "Intermediate"</t>
+  </si>
+  <si>
+    <t>The skill should be updated successfully, and a confirmation message should appear: "JavaScript" has been updated to your skills.</t>
+  </si>
+  <si>
+    <t>User can delete a skill</t>
+  </si>
+  <si>
+    <t>Verify that a user can delete a skill from their profile.</t>
+  </si>
+  <si>
+    <t>1. Click on the 'Delete' icon next to a skill.
+2. Confirm the deletion.</t>
+  </si>
+  <si>
+    <t>Skill Name: "Java"</t>
+  </si>
+  <si>
+    <t>The skill should be deleted, and a confirmation message should appear: "Java" has been deleted.</t>
+  </si>
+  <si>
+    <t>User can add multiple skills</t>
+  </si>
+  <si>
+    <t>Verify that a user can add as many skills as they want.</t>
+  </si>
+  <si>
+    <t>User is logged in and on the Skills tab.</t>
+  </si>
+  <si>
+    <t>Add multiple skills.</t>
+  </si>
+  <si>
+    <t>Skill Names: "Java", "Python", "SQL"
+Skill Levels: "Advanced", "Beginner", "Intermediate"</t>
+  </si>
+  <si>
+    <t>The user should be able to add unlimited skills.</t>
+  </si>
+  <si>
+    <t>Adding empty skill</t>
+  </si>
+  <si>
+    <t>Verify that an error message is shown when trying to add an empty skill.</t>
+  </si>
+  <si>
+    <t>User is on the Skills tab.</t>
+  </si>
+  <si>
+    <t>1. Click on 'Add New'.
+2. Leave the skill name or level empty.
+3. Click on 'Add'.</t>
+  </si>
+  <si>
+    <t>Skill Name: ""
+Skill Level: "Beginner"</t>
+  </si>
+  <si>
+    <t>The skill should not be added, and an error message should appear: "Please enter skill and experience level."</t>
+  </si>
+  <si>
+    <t>Adding same skill and level</t>
+  </si>
+  <si>
+    <t>Verify that an error message is shown when trying to add the same skill with the same level.</t>
+  </si>
+  <si>
+    <t>User is on the Skills tab and has existing skills.</t>
+  </si>
+  <si>
+    <t>1. Click on 'Add New'.
+2. Enter a skill that already exists with the same level.
+3. Click on 'Add'.</t>
+  </si>
+  <si>
+    <t>The skill should not be added, and an error message should appear: "This skill is already exist in your skill list."</t>
+  </si>
+  <si>
+    <t>Adding same skill but different level</t>
+  </si>
+  <si>
+    <t>Verify that an error message is shown when trying to add the same skill with a different level.</t>
+  </si>
+  <si>
+    <t>1. Click on 'Add New'.
+2. Enter a skill that already exists with a different level.
+3. Click on 'Add'.</t>
+  </si>
+  <si>
+    <t>Skill Name: "Java"
+Skill Level: "Beginner"</t>
+  </si>
+  <si>
+    <t>The skill should not be added, and an error message should appear: "Duplicated data."</t>
+  </si>
+  <si>
+    <t>User cannot add a skill when clicked "Cancel"</t>
+  </si>
+  <si>
+    <t>Verify that a user cannot add a skill when clicked "Cancel"</t>
+  </si>
+  <si>
+    <t>1. Click on 'Add New'.
+2. Enter a skill name.
+3. Select the skill level.
+4. Click on 'Cancel'.</t>
+  </si>
+  <si>
+    <t>The skill should not be added.</t>
+  </si>
+  <si>
+    <t>User cannot edit a skill when clicked "Cancel"</t>
+  </si>
+  <si>
+    <t>Verify that a user cannot edit a skill name and level.</t>
+  </si>
+  <si>
+    <t>1. Click on the 'Edit' icon next to an existing skill.
+2. Edit the skill name and level.
+3. Click on 'Cancel'.</t>
+  </si>
+  <si>
+    <t>The skill should not be updated and the text boxes should disappear.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -40,19 +425,174 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF242424"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="11">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -61,13 +601,378 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="12">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" wrapText="0"/>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+      <alignment horizontal="left" vertical="top" wrapText="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" wrapText="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" wrapText="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -78,6 +983,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F8A4C556-379B-4103-8514-50B149F554F8}" name="Table1" displayName="Table1" ref="A1:H10" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10" headerRowBorderDxfId="8" tableBorderDxfId="9">
+  <autoFilter ref="A1:H10" xr:uid="{F8A4C556-379B-4103-8514-50B149F554F8}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{9D25D1D8-D068-4420-9BC6-AB8A3BA959D9}" name="Test Case ID" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{D4D33C50-7E41-4C43-8A28-7E62AEDB14E5}" name="Test Case Title" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{B6EFFCF8-50B5-4A55-86E3-40753DF9FE45}" name="Description" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{42CDE058-BD8B-423C-A92B-CBD104692401}" name="Preconditions" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{960588EC-70B5-4884-89B3-09411DBEB237}" name="Test Steps" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{F88F27F2-3378-4790-934B-50901B6D6A76}" name="Test Data" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{079E76A8-5DEA-4996-B3D7-24018AD4C13F}" name="Expected Results" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{87BDAB71-D1DF-4E5B-9E92-416A5EDAFFD1}" name="Status" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -396,10 +1318,565 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A5778BF-406A-49CD-AA09-814FF2E01C6D}">
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="14.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="104.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="129.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="74.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="44.7109375" style="5" customWidth="1"/>
+    <col min="7" max="7" width="150.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="2"/>
+    <col min="9" max="16384" width="9.140625" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="16.5">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="64.5">
+      <c r="A2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="60" customHeight="1">
+      <c r="A3" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="33.75" customHeight="1">
+      <c r="A4" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="76.5" customHeight="1">
+      <c r="A5" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="113.25">
+      <c r="A6" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="76.5" customHeight="1">
+      <c r="A7" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="75" customHeight="1">
+      <c r="A8" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="144.75" customHeight="1">
+      <c r="A9" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="48.75">
+      <c r="A10" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5107047-3286-4FF8-9E7B-C8E4F426817E}">
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="87.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.28515625" customWidth="1"/>
+    <col min="7" max="7" width="121" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15.75">
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="113.25">
+      <c r="A2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="113.25">
+      <c r="A3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="98.25" customHeight="1">
+      <c r="A4" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="64.5">
+      <c r="A5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="96.75">
+      <c r="A6" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="96.75">
+      <c r="A7" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="96.75">
+      <c r="A8" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="126" customHeight="1">
+      <c r="A9" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="137.25" customHeight="1">
+      <c r="A10" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>